--- a/artfynd/A 49872-2021 artfynd.xlsx
+++ b/artfynd/A 49872-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49872-2021 artfynd.xlsx
+++ b/artfynd/A 49872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96416166</v>
+        <v>96416143</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555730.8204813726</v>
+        <v>555726</v>
       </c>
       <c r="R2" t="n">
-        <v>6697154.358772255</v>
+        <v>6697146</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100-tal bladrosetter</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,52 +792,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96416389</v>
+        <v>96416497</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555765.8940561407</v>
+        <v>555772</v>
       </c>
       <c r="R3" t="n">
-        <v>6697319.94286498</v>
+        <v>6697336</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,52 +900,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96416196</v>
+        <v>96416576</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555694.0420504911</v>
+        <v>555787</v>
       </c>
       <c r="R4" t="n">
-        <v>6697164.171555474</v>
+        <v>6697364</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,12 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>11 blomstänglar, 100-tal bladrosetter</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,19 +1017,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96416143</v>
+        <v>96417143</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1052,24 +1037,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555725.9933004811</v>
+        <v>555770</v>
       </c>
       <c r="R5" t="n">
-        <v>6697146.378104035</v>
+        <v>6697144</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,19 +1125,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96416576</v>
+        <v>96417255</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1174,24 +1145,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1199,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555787.4856440008</v>
+        <v>555773</v>
       </c>
       <c r="R6" t="n">
-        <v>6697364.252592626</v>
+        <v>6697084</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,51 +1233,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96417255</v>
+        <v>96416152</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555772.9789894398</v>
+        <v>555726</v>
       </c>
       <c r="R7" t="n">
-        <v>6697084.340921767</v>
+        <v>6697146</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1319,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>50-tal bladrosetter, 2 blomstänglar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,15 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96416889</v>
+        <v>96416166</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555770.1080124292</v>
+        <v>555731</v>
       </c>
       <c r="R8" t="n">
-        <v>6697238.968303593</v>
+        <v>6697155</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1433,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,15 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96416152</v>
+        <v>96416196</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,11 +1494,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1544,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555725.9933004811</v>
+        <v>555694</v>
       </c>
       <c r="R9" t="n">
-        <v>6697146.378104035</v>
+        <v>6697164</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1579,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1547,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>50-tal bladrosetter, 2 blomstänglar</t>
+          <t>11 blomstänglar, 100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,51 +1579,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96417143</v>
+        <v>96416211</v>
       </c>
       <c r="B10" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555770.0809884217</v>
+        <v>555713</v>
       </c>
       <c r="R10" t="n">
-        <v>6697144.090305033</v>
+        <v>6697230</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1697,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,51 +1693,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96416497</v>
+        <v>96416389</v>
       </c>
       <c r="B11" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555771.5891082257</v>
+        <v>555766</v>
       </c>
       <c r="R11" t="n">
-        <v>6697335.842714685</v>
+        <v>6697319</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1810,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,15 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96417067</v>
+        <v>96416889</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555777.8164671068</v>
+        <v>555770</v>
       </c>
       <c r="R12" t="n">
-        <v>6697156.06900642</v>
+        <v>6697239</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1924,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,12 +1914,7 @@
         <v>96417037</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555781.3880673081</v>
+        <v>555781</v>
       </c>
       <c r="R13" t="n">
-        <v>6697181.325914091</v>
+        <v>6697181</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2084,37 +2029,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96417217</v>
+        <v>96417067</v>
       </c>
       <c r="B14" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2126,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555763.5704732356</v>
+        <v>555778</v>
       </c>
       <c r="R14" t="n">
-        <v>6697116.811344855</v>
+        <v>6697156</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2161,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,12 +2141,7 @@
         <v>96417130</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555770.0809884217</v>
+        <v>555770</v>
       </c>
       <c r="R15" t="n">
-        <v>6697144.090305033</v>
+        <v>6697144</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2312,61 +2247,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96416786</v>
+        <v>99590640</v>
       </c>
       <c r="B16" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Husby, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555785.8518649261</v>
+        <v>555758</v>
       </c>
       <c r="R16" t="n">
-        <v>6697245.140026065</v>
+        <v>6697338</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2393,22 +2323,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-02</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-02</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,52 +2358,56 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96416211</v>
+        <v>96416786</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2477,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555712.8427286618</v>
+        <v>555786</v>
       </c>
       <c r="R17" t="n">
-        <v>6697229.194148478</v>
+        <v>6697245</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2512,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2522,12 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>100-tal bladrosetter</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,15 +2476,124 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96417217</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555763</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6697117</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49872-2021 artfynd.xlsx
+++ b/artfynd/A 49872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416576</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96417143</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96417255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416152</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416166</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416196</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1690,6 +1735,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416211</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416389</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416889</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96417037</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2135,6 +2200,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96417067</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2244,6 +2314,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96417130</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99590640</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2485,6 +2565,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96416786</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2594,8 +2679,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96417217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>